--- a/translations/welsh-translations/xlsx/18-obligations-home.xlsx
+++ b/translations/welsh-translations/xlsx/18-obligations-home.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="161">
   <si>
     <t>Translator notes</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Manage your recycling obligations</t>
   </si>
   <si>
+    <t>Rheoli'ch rhwymedigaethau ailgylchu</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -61,46 +64,70 @@
     <t>Manage your {{year}} recycling obligations</t>
   </si>
   <si>
+    <t>Rheoli'ch rhwymedigaethau ailgylchu ar gyfer {{year}}</t>
+  </si>
+  <si>
     <t>obligations.home.producerLabel</t>
   </si>
   <si>
     <t>Producer:</t>
   </si>
   <si>
+    <t>Cynhyrchydd:</t>
+  </si>
+  <si>
     <t>obligations.home.complianceSchemeLabel</t>
   </si>
   <si>
     <t>Compliance scheme:</t>
   </si>
   <si>
+    <t>Cynllun cydymffurfio:</t>
+  </si>
+  <si>
     <t>obligations.home.regulatorLabel</t>
   </si>
   <si>
     <t>Regulator:</t>
   </si>
   <si>
+    <t>Rheoleiddiwr:</t>
+  </si>
+  <si>
     <t>obligations.home.regulatorEngland</t>
   </si>
   <si>
-    <t>Environment Agency (England)</t>
+    <t>Environment Agency</t>
+  </si>
+  <si>
+    <t>Asiantaeth yr Amgylchedd (EA)</t>
   </si>
   <si>
     <t>obligations.home.regulatorScotland</t>
   </si>
   <si>
-    <t>Scottish Environment Protection Agency (Scotland)</t>
+    <t>Scottish Environment Protection Agency</t>
+  </si>
+  <si>
+    <t>Asiantaeth Diogelu Amgylchedd yr Alban (SEPA)</t>
   </si>
   <si>
     <t>obligations.home.regulatorWales</t>
   </si>
   <si>
-    <t>Natural Resources Wales (Wales)</t>
+    <t>Natural Resources Wales</t>
+  </si>
+  <si>
+    <t>Cyfoeth Naturiol Cymru (CNC)</t>
   </si>
   <si>
     <t>obligations.home.regulatorNorthernIreland</t>
   </si>
   <si>
-    <t>Northern Ireland Environment Agency (Northern Ireland)</t>
+    <t>Northern Ireland Environment Agency</t>
+  </si>
+  <si>
+    <t>Asiantaeth Amgylchedd Gogledd Iwerddon (NIEA)</t>
   </si>
   <si>
     <t>obligations.home.deadlineText</t>
@@ -109,124 +136,187 @@
     <t>You have until</t>
   </si>
   <si>
+    <t>Mae gennych chi tan</t>
+  </si>
+  <si>
     <t>obligations.home.deadlineDateBold</t>
   </si>
   <si>
     <t>31 January {{deadlineYear}}</t>
   </si>
   <si>
+    <t>31 Ionawr {{deadlineYear}}</t>
+  </si>
+  <si>
     <t>obligations.home.deadlineTextSuffix</t>
   </si>
   <si>
     <t>to meet your recycling obligations for {{year}}.</t>
   </si>
   <si>
+    <t>i gyflawni'ch rhwymedigaethau ailgylchu ar gyfer {{year}}.</t>
+  </si>
+  <si>
     <t>obligations.home.enforcementWarning</t>
   </si>
   <si>
     <t>You may face enforcement action if you miss this deadline.</t>
   </si>
   <si>
+    <t>Os collwch chi'r dyddiad cau yma, fe allech chi wynebu camau gorfodi.</t>
+  </si>
+  <si>
     <t>obligations.home.awaitingAcceptanceLabel</t>
   </si>
   <si>
     <t>Number of PRNs and PERNs awaiting acceptance.</t>
   </si>
   <si>
+    <t>Nifer y PRNs a'r PERNs sy'n aros i gael eu derbyn</t>
+  </si>
+  <si>
     <t>obligations.home.acceptRejectLink</t>
   </si>
   <si>
     <t>Accept or reject PRNs and PERNs</t>
   </si>
   <si>
+    <t>Derbyn neu wrthod PRNs a PERNs</t>
+  </si>
+  <si>
     <t>obligations.home.howToMeetHeading</t>
   </si>
   <si>
     <t>How to meet your recycling obligations</t>
   </si>
   <si>
+    <t>Sut i gyflawni'ch rhwymedigaethau ailgylchu ar gyfer</t>
+  </si>
+  <si>
     <t>obligations.home.howToMeetParagraph</t>
   </si>
   <si>
     <t>Acquire and accept packaging waste recycling notes (PRNs) and packaging waste export recycling notes (PERNs) until your recycling obligations are fully met. Select a material for information on how the data was calculated and view your progress towards meeting your {{year}} recycling obligations.</t>
   </si>
   <si>
+    <t>Ewch ati i gaffael a derbyn nodiadau ailgylchu gwastraff pecynwaith (PRNs) a nodiadau ailgylchu allforio gwastraff pecynwaith (PERNs) nes bod eich rhwymedigaethau ailgylchu wedi'u bodloni'n llawn. Dewiswch ddeunydd i gael gwybodaeth am sut y cyfrifwyd y data a gweld eich cynnydd tuag at fodloni’ch rhwymedigaethau ailgylchu {{year}}.</t>
+  </si>
+  <si>
     <t>obligations.home.obligationsProgressCaption</t>
   </si>
   <si>
     <t>Your recycling obligations progress</t>
   </si>
   <si>
+    <t>Cynnydd eich rhwymedigaethau ailgylchu</t>
+  </si>
+  <si>
     <t>obligations.home.glassHeading</t>
   </si>
   <si>
     <t>How to meet the glass recycling obligation</t>
   </si>
   <si>
+    <t>Sut i gyflawni'r rhwymedigaeth ailgylchu gwydr</t>
+  </si>
+  <si>
     <t>obligations.home.glassDescription</t>
   </si>
   <si>
     <t>A minimum of {{glassTarget}}% of your glass recycling obligation must be made up of glass re-melt PRNs or PERNs. This will make up a proportion of your overall glass recycling obligation. The remaining glass recycling obligation can be met by either glass re-melt, glass other or a mix of both.</t>
   </si>
   <si>
+    <t>Rhaid i {{glassTarget}}% o leiaf o'ch rhwymedigaeth ailgylchu gwydr fod yn PRNs neu PERNs gwydr aildoddi. Bydd hyn yn ffurfio cyfran o gyfanswm eich rhwymedigaeth ailgylchu gwydr. Gall gweddill y rhwymedigaeth ailgylchu gwydr gael ei gyflawni ar ffurf gwydr aildoddi, gwydr arall neu gymysgedd o'r ddau.</t>
+  </si>
+  <si>
     <t>obligations.home.glassBreakdownCaption</t>
   </si>
   <si>
     <t>Glass recycling obligation breakdown</t>
   </si>
   <si>
+    <t>Dadansoddiad o'r rhwymedigaeth ailgylchu gwydr</t>
+  </si>
+  <si>
     <t>obligations.home.whatToDoNextHeading</t>
   </si>
   <si>
     <t>What to do next</t>
   </si>
   <si>
+    <t>Beth i'w wneud nesaf</t>
+  </si>
+  <si>
     <t>obligations.home.reviewPrnsHeading</t>
   </si>
   <si>
     <t>Review your PRNs and PERNs for {{year}}</t>
   </si>
   <si>
+    <t>Adolygu’ch PRNs a’ch PERNs ar gyfer {{year}}</t>
+  </si>
+  <si>
     <t>obligations.home.reviewPrnsParagraph</t>
   </si>
   <si>
     <t>View and accept any issued PRNs and PERNs to meet your recycling obligations.</t>
   </si>
   <si>
+    <t>Gweld a derbyn unrhyw PRNs a PERNs sydd wedi'u rhoi er mwyn cyflawni'ch rhwymedigaethau ailgylchu.</t>
+  </si>
+  <si>
     <t>obligations.home.acceptRejectYearLink</t>
   </si>
   <si>
     <t>Accept or reject PRNs and PERNs for {{year}}</t>
   </si>
   <si>
+    <t>Derbyn neu wrthod PRNs a PERNs ar gyfer {{year}}</t>
+  </si>
+  <si>
     <t>obligations.home.searchLink</t>
   </si>
   <si>
     <t>Search PRNs and PERNs</t>
   </si>
   <si>
+    <t>Chwilio PRNs a PERNs</t>
+  </si>
+  <si>
     <t>obligations.home.downloadLink</t>
   </si>
   <si>
     <t>Download a list of your PRNs and PERNs for {{year}} (CSV)</t>
   </si>
   <si>
+    <t>Lawrlwythwch restr o'ch PRNs a’ch PERNs ar gyfer {{year}} (CSV)</t>
+  </si>
+  <si>
     <t>obligations.home.submitCertificateHeading</t>
   </si>
   <si>
     <t>Submit your certificate of compliance</t>
   </si>
   <si>
+    <t>Cyflwyno eich tystysgrif cydymffurfio</t>
+  </si>
+  <si>
     <t>obligations.home.submitCertificateParagraphPrefix</t>
   </si>
   <si>
     <t>An approved or delegated person must submit your {{year}} certificate of compliance before or on</t>
   </si>
   <si>
+    <t>Rhaid i berson cymeradwy neu ddirprwyedig gyflwyno eich {{year}} datganiad cydymffurfio ar</t>
+  </si>
+  <si>
     <t>obligations.home.submitCertificateButton</t>
   </si>
   <si>
-    <t>Submit certificate</t>
+    <t>Submit your certificate</t>
+  </si>
+  <si>
+    <t>Cyflwyno eich tystysgrif</t>
   </si>
   <si>
     <t>obligations.home.submitStatementHeading</t>
@@ -235,6 +325,9 @@
     <t>Submit your statement of compliance</t>
   </si>
   <si>
+    <t>Cyflwyno eich datganiad cydymffurfio</t>
+  </si>
+  <si>
     <t>obligations.home.submitStatementParagraphPrefix</t>
   </si>
   <si>
@@ -244,7 +337,163 @@
     <t>obligations.home.submitStatementButton</t>
   </si>
   <si>
-    <t>Submit statement</t>
+    <t>Submit your statement</t>
+  </si>
+  <si>
+    <t>Cyflwyno eich datganiad</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedCertificateHeading</t>
+  </si>
+  <si>
+    <t>View your certificate of compliance</t>
+  </si>
+  <si>
+    <t>Gweld eich tystysgrif cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedCertificateParagraph</t>
+  </si>
+  <si>
+    <t>Your {{year}} certificate of compliance has been submitted.</t>
+  </si>
+  <si>
+    <t>Mae eich {{year}} tystysgrif cydymffurfio wedi’i chyflwyno.</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedStatementHeading</t>
+  </si>
+  <si>
+    <t>View your statement of compliance</t>
+  </si>
+  <si>
+    <t>Gweld eich datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedStatementParagraph</t>
+  </si>
+  <si>
+    <t>Your {{year}} statement of compliance has been submitted.</t>
+  </si>
+  <si>
+    <t>Mae eich {{year}} datganiad cydymffurfio wedi’i gyflwyno.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>You missed the certificate of compliance deadline</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>You missed the submission deadline of 31 January {{year}}. You can no longer submit your {{yearBefore}} certificate of compliance.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>The {{regulator}} will contact you to discuss what happens next.</t>
+  </si>
+  <si>
+    <t>obligations.home.statementMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>You missed the statement of compliance deadline</t>
+  </si>
+  <si>
+    <t>obligations.home.statementMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>You missed the submission deadline of 31 January {{year}}. You can no longer submit your {{yearBefore}} statement of compliance.</t>
+  </si>
+  <si>
+    <t>obligations.home.statementMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledHeading</t>
+  </si>
+  <si>
+    <t>Resubmit your certificate of compliance</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich tystysgrif cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledParagraph</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} certificate of compliance. An approved or delegated person must resubmit your certificate on or before 31 January {{futureYear}}.</t>
+  </si>
+  <si>
+    <t>Mae {{regulator}} wedi canslo eich {1} tystysgrif cydymffurfio. Rhaid i berson cymeradwy neu ddirprwyedig gyflwyno eich tystysgrif ar 31 Ionawr {{yyyy}} neu cyn hynny.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledButtonLabel</t>
+  </si>
+  <si>
+    <t>Resubmit your certificate</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich tystysgrif</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledHeading</t>
+  </si>
+  <si>
+    <t>Resubmit your statement of compliance</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledParagraph</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} statement of compliance. An approved or delegated person must resubmit your statement on or before 31 January {{futureYear}}.</t>
+  </si>
+  <si>
+    <t>Mae {{regulator}} wedi canslo eich {1} datganiad cydymffurfio. Rhaid i berson cymeradwy neu ddirprwyedig ailgyflwyno eich datganiad ar 31 Ionawr {{yyyy}} neu cyn hynny..</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledButtonLabel</t>
+  </si>
+  <si>
+    <t>Resubmit your statement</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich datganiad</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} certificate of compliance.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>As the deadline of 31 January {{year}} has now passed, you can no longer resubmit your certificate. The {{regulator}} will contact you to discuss what happens next.</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} statement of compliance.</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>As the deadline of 31 January {{year}} has now passed, you can no longer resubmit your statement. The {{regulator}} will contact you to discuss what happens next.</t>
   </si>
 </sst>
 </file>
@@ -643,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -711,12 +960,12 @@
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -725,18 +974,18 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -745,18 +994,18 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -765,18 +1014,18 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -785,18 +1034,18 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -805,18 +1054,18 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -825,18 +1074,18 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -845,18 +1094,18 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -865,18 +1114,18 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>10</v>
@@ -885,18 +1134,18 @@
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
@@ -905,18 +1154,18 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>10</v>
@@ -925,18 +1174,18 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>10</v>
@@ -945,18 +1194,18 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>10</v>
@@ -965,18 +1214,18 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>10</v>
@@ -985,18 +1234,18 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>10</v>
@@ -1005,18 +1254,18 @@
         <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" ht="118" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" ht="136" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>10</v>
@@ -1025,18 +1274,18 @@
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>10</v>
@@ -1045,18 +1294,18 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>10</v>
@@ -1065,18 +1314,18 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" ht="118" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>10</v>
@@ -1085,18 +1334,18 @@
         <v>11</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>10</v>
@@ -1105,18 +1354,18 @@
         <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>10</v>
@@ -1125,18 +1374,18 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>10</v>
@@ -1145,18 +1394,18 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>10</v>
@@ -1165,18 +1414,18 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>10</v>
@@ -1185,18 +1434,18 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
@@ -1205,18 +1454,18 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>10</v>
@@ -1225,18 +1474,18 @@
         <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
@@ -1245,18 +1494,18 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
@@ -1265,18 +1514,18 @@
         <v>11</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>10</v>
@@ -1285,18 +1534,18 @@
         <v>11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>10</v>
@@ -1305,18 +1554,18 @@
         <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
@@ -1325,18 +1574,18 @@
         <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>10</v>
@@ -1345,17 +1594,457 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F38"/>
+  <autoFilter ref="A5:F60"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>

--- a/translations/welsh-translations/xlsx/18-obligations-home.xlsx
+++ b/translations/welsh-translations/xlsx/18-obligations-home.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="160">
   <si>
     <t>Translator notes</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Manage your recycling obligations</t>
   </si>
   <si>
+    <t>Rheoli'ch rhwymedigaethau ailgylchu</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -61,46 +64,70 @@
     <t>Manage your {{year}} recycling obligations</t>
   </si>
   <si>
+    <t>Rheoli'ch rhwymedigaethau ailgylchu ar gyfer {{year}}</t>
+  </si>
+  <si>
     <t>obligations.home.producerLabel</t>
   </si>
   <si>
     <t>Producer:</t>
   </si>
   <si>
+    <t>Cynhyrchydd:</t>
+  </si>
+  <si>
     <t>obligations.home.complianceSchemeLabel</t>
   </si>
   <si>
     <t>Compliance scheme:</t>
   </si>
   <si>
+    <t>Cynllun cydymffurfio:</t>
+  </si>
+  <si>
     <t>obligations.home.regulatorLabel</t>
   </si>
   <si>
     <t>Regulator:</t>
   </si>
   <si>
+    <t>Rheoleiddiwr:</t>
+  </si>
+  <si>
     <t>obligations.home.regulatorEngland</t>
   </si>
   <si>
-    <t>Environment Agency (England)</t>
+    <t>Environment Agency</t>
+  </si>
+  <si>
+    <t>Asiantaeth yr Amgylchedd (EA)</t>
   </si>
   <si>
     <t>obligations.home.regulatorScotland</t>
   </si>
   <si>
-    <t>Scottish Environment Protection Agency (Scotland)</t>
+    <t>Scottish Environment Protection Agency</t>
+  </si>
+  <si>
+    <t>Asiantaeth Diogelu Amgylchedd yr Alban (SEPA)</t>
   </si>
   <si>
     <t>obligations.home.regulatorWales</t>
   </si>
   <si>
-    <t>Natural Resources Wales (Wales)</t>
+    <t>Natural Resources Wales</t>
+  </si>
+  <si>
+    <t>Cyfoeth Naturiol Cymru (CNC)</t>
   </si>
   <si>
     <t>obligations.home.regulatorNorthernIreland</t>
   </si>
   <si>
-    <t>Northern Ireland Environment Agency (Northern Ireland)</t>
+    <t>Northern Ireland Environment Agency</t>
+  </si>
+  <si>
+    <t>Asiantaeth Amgylchedd Gogledd Iwerddon (NIEA)</t>
   </si>
   <si>
     <t>obligations.home.deadlineText</t>
@@ -109,124 +136,187 @@
     <t>You have until</t>
   </si>
   <si>
+    <t>Mae gennych chi tan</t>
+  </si>
+  <si>
     <t>obligations.home.deadlineDateBold</t>
   </si>
   <si>
     <t>31 January {{deadlineYear}}</t>
   </si>
   <si>
+    <t>31 Ionawr {{deadlineYear}}</t>
+  </si>
+  <si>
     <t>obligations.home.deadlineTextSuffix</t>
   </si>
   <si>
     <t>to meet your recycling obligations for {{year}}.</t>
   </si>
   <si>
+    <t>i gyflawni'ch rhwymedigaethau ailgylchu ar gyfer {{year}}.</t>
+  </si>
+  <si>
     <t>obligations.home.enforcementWarning</t>
   </si>
   <si>
     <t>You may face enforcement action if you miss this deadline.</t>
   </si>
   <si>
+    <t>Os collwch chi'r dyddiad cau yma, fe allech chi wynebu camau gorfodi.</t>
+  </si>
+  <si>
     <t>obligations.home.awaitingAcceptanceLabel</t>
   </si>
   <si>
     <t>Number of PRNs and PERNs awaiting acceptance.</t>
   </si>
   <si>
+    <t>Nifer y PRNs a'r PERNs sy'n aros i gael eu derbyn</t>
+  </si>
+  <si>
     <t>obligations.home.acceptRejectLink</t>
   </si>
   <si>
     <t>Accept or reject PRNs and PERNs</t>
   </si>
   <si>
+    <t>Derbyn neu wrthod PRNs a PERNs</t>
+  </si>
+  <si>
     <t>obligations.home.howToMeetHeading</t>
   </si>
   <si>
     <t>How to meet your recycling obligations</t>
   </si>
   <si>
+    <t>Sut i gyflawni'ch rhwymedigaethau ailgylchu ar gyfer</t>
+  </si>
+  <si>
     <t>obligations.home.howToMeetParagraph</t>
   </si>
   <si>
     <t>Acquire and accept packaging waste recycling notes (PRNs) and packaging waste export recycling notes (PERNs) until your recycling obligations are fully met. Select a material for information on how the data was calculated and view your progress towards meeting your {{year}} recycling obligations.</t>
   </si>
   <si>
+    <t>Ewch ati i gaffael a derbyn nodiadau ailgylchu gwastraff pecynwaith (PRNs) a nodiadau ailgylchu allforio gwastraff pecynwaith (PERNs) nes bod eich rhwymedigaethau ailgylchu wedi'u bodloni'n llawn. Dewiswch ddeunydd i gael gwybodaeth am sut y cyfrifwyd y data a gweld eich cynnydd tuag at fodloni’ch rhwymedigaethau ailgylchu {{year}}.</t>
+  </si>
+  <si>
     <t>obligations.home.obligationsProgressCaption</t>
   </si>
   <si>
     <t>Your recycling obligations progress</t>
   </si>
   <si>
+    <t>Cynnydd eich rhwymedigaethau ailgylchu</t>
+  </si>
+  <si>
     <t>obligations.home.glassHeading</t>
   </si>
   <si>
     <t>How to meet the glass recycling obligation</t>
   </si>
   <si>
+    <t>Sut i gyflawni'r rhwymedigaeth ailgylchu gwydr</t>
+  </si>
+  <si>
     <t>obligations.home.glassDescription</t>
   </si>
   <si>
     <t>A minimum of {{glassTarget}}% of your glass recycling obligation must be made up of glass re-melt PRNs or PERNs. This will make up a proportion of your overall glass recycling obligation. The remaining glass recycling obligation can be met by either glass re-melt, glass other or a mix of both.</t>
   </si>
   <si>
+    <t>Rhaid i {{glassTarget}}% o leiaf o'ch rhwymedigaeth ailgylchu gwydr fod yn PRNs neu PERNs gwydr aildoddi. Bydd hyn yn ffurfio cyfran o gyfanswm eich rhwymedigaeth ailgylchu gwydr. Gall gweddill y rhwymedigaeth ailgylchu gwydr gael ei gyflawni ar ffurf gwydr aildoddi, gwydr arall neu gymysgedd o'r ddau.</t>
+  </si>
+  <si>
     <t>obligations.home.glassBreakdownCaption</t>
   </si>
   <si>
     <t>Glass recycling obligation breakdown</t>
   </si>
   <si>
+    <t>Dadansoddiad o'r rhwymedigaeth ailgylchu gwydr</t>
+  </si>
+  <si>
     <t>obligations.home.whatToDoNextHeading</t>
   </si>
   <si>
     <t>What to do next</t>
   </si>
   <si>
+    <t>Beth i'w wneud nesaf</t>
+  </si>
+  <si>
     <t>obligations.home.reviewPrnsHeading</t>
   </si>
   <si>
     <t>Review your PRNs and PERNs for {{year}}</t>
   </si>
   <si>
+    <t>Adolygu’ch PRNs a’ch PERNs ar gyfer {{year}}</t>
+  </si>
+  <si>
     <t>obligations.home.reviewPrnsParagraph</t>
   </si>
   <si>
     <t>View and accept any issued PRNs and PERNs to meet your recycling obligations.</t>
   </si>
   <si>
+    <t>Gweld a derbyn unrhyw PRNs a PERNs sydd wedi'u rhoi er mwyn cyflawni'ch rhwymedigaethau ailgylchu.</t>
+  </si>
+  <si>
     <t>obligations.home.acceptRejectYearLink</t>
   </si>
   <si>
     <t>Accept or reject PRNs and PERNs for {{year}}</t>
   </si>
   <si>
+    <t>Derbyn neu wrthod PRNs a PERNs ar gyfer {{year}}</t>
+  </si>
+  <si>
     <t>obligations.home.searchLink</t>
   </si>
   <si>
     <t>Search PRNs and PERNs</t>
   </si>
   <si>
+    <t>Chwilio PRNs a PERNs</t>
+  </si>
+  <si>
     <t>obligations.home.downloadLink</t>
   </si>
   <si>
     <t>Download a list of your PRNs and PERNs for {{year}} (CSV)</t>
   </si>
   <si>
+    <t>Lawrlwythwch restr o'ch PRNs a’ch PERNs ar gyfer {{year}} (CSV)</t>
+  </si>
+  <si>
     <t>obligations.home.submitCertificateHeading</t>
   </si>
   <si>
     <t>Submit your certificate of compliance</t>
   </si>
   <si>
+    <t>Cyflwyno eich tystysgrif cydymffurfio</t>
+  </si>
+  <si>
     <t>obligations.home.submitCertificateParagraphPrefix</t>
   </si>
   <si>
     <t>An approved or delegated person must submit your {{year}} certificate of compliance before or on</t>
   </si>
   <si>
+    <t>Rhaid i berson cymeradwy neu ddirprwyedig gyflwyno eich {{year}} datganiad cydymffurfio ar</t>
+  </si>
+  <si>
     <t>obligations.home.submitCertificateButton</t>
   </si>
   <si>
-    <t>Submit certificate</t>
+    <t>Submit your certificate</t>
+  </si>
+  <si>
+    <t>Cyflwyno eich tystysgrif</t>
   </si>
   <si>
     <t>obligations.home.submitStatementHeading</t>
@@ -235,6 +325,9 @@
     <t>Submit your statement of compliance</t>
   </si>
   <si>
+    <t>Cyflwyno eich datganiad cydymffurfio</t>
+  </si>
+  <si>
     <t>obligations.home.submitStatementParagraphPrefix</t>
   </si>
   <si>
@@ -244,7 +337,160 @@
     <t>obligations.home.submitStatementButton</t>
   </si>
   <si>
-    <t>Submit statement</t>
+    <t>Submit your statement</t>
+  </si>
+  <si>
+    <t>Cyflwyno eich datganiad</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedCertificateHeading</t>
+  </si>
+  <si>
+    <t>View your certificate of compliance</t>
+  </si>
+  <si>
+    <t>Gweld eich tystysgrif cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedCertificateParagraph</t>
+  </si>
+  <si>
+    <t>Your {{year}} certificate of compliance has been submitted.</t>
+  </si>
+  <si>
+    <t>Mae eich {{year}} tystysgrif cydymffurfio wedi’i chyflwyno.</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedStatementHeading</t>
+  </si>
+  <si>
+    <t>View your statement of compliance</t>
+  </si>
+  <si>
+    <t>Gweld eich datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.submittedStatementParagraph</t>
+  </si>
+  <si>
+    <t>Your {{year}} statement of compliance has been submitted.</t>
+  </si>
+  <si>
+    <t>Mae eich {{year}} datganiad cydymffurfio wedi’i gyflwyno.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>You missed the certificate of compliance deadline</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>You missed the submission deadline of 31 January {{year}}. You can no longer submit your {{yearBefore}} certificate of compliance.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>The {{regulator}} will contact you to discuss what happens next.</t>
+  </si>
+  <si>
+    <t>obligations.home.statementMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>You missed the statement of compliance deadline</t>
+  </si>
+  <si>
+    <t>obligations.home.statementMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>obligations.home.statementMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledHeading</t>
+  </si>
+  <si>
+    <t>Resubmit your certificate of compliance</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich tystysgrif cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledParagraph</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} certificate of compliance. An approved or delegated person must resubmit your certificate on or before 31 January {{futureYear}}.</t>
+  </si>
+  <si>
+    <t>Mae {{regulator}} wedi canslo eich {1} tystysgrif cydymffurfio. Rhaid i berson cymeradwy neu ddirprwyedig gyflwyno eich tystysgrif ar 31 Ionawr {{yyyy}} neu cyn hynny.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledButtonLabel</t>
+  </si>
+  <si>
+    <t>Resubmit your certificate</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich tystysgrif</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledHeading</t>
+  </si>
+  <si>
+    <t>Resubmit your statement of compliance</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledParagraph</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} statement of compliance. An approved or delegated person must resubmit your statement on or before 31 January {{futureYear}}.</t>
+  </si>
+  <si>
+    <t>Mae {{regulator}} wedi canslo eich {1} datganiad cydymffurfio. Rhaid i berson cymeradwy neu ddirprwyedig ailgyflwyno eich datganiad ar 31 Ionawr {{yyyy}} neu cyn hynny..</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledButtonLabel</t>
+  </si>
+  <si>
+    <t>Resubmit your statement</t>
+  </si>
+  <si>
+    <t>Ailgyflwyno eich datganiad</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} certificate of compliance.</t>
+  </si>
+  <si>
+    <t>obligations.home.certificateCancelledMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>As the deadline of 31 January {{year}} has now passed, you can no longer resubmit your certificate. The {{regulator}} will contact you to discuss what happens next.</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledMissedDeadlineHeading</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>The {{regulator}} cancelled your {{year}} statement of compliance.</t>
+  </si>
+  <si>
+    <t>obligations.home.statementCancelledMissedDeadlineParagraphSuffix</t>
+  </si>
+  <si>
+    <t>As the deadline of 31 January {{year}} has now passed, you can no longer resubmit your statement. The {{regulator}} will contact you to discuss what happens next.</t>
   </si>
 </sst>
 </file>
@@ -643,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -711,12 +957,12 @@
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -725,18 +971,18 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -745,18 +991,18 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -765,18 +1011,18 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -785,18 +1031,18 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -805,18 +1051,18 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -825,18 +1071,18 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -845,18 +1091,18 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -865,18 +1111,18 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>10</v>
@@ -885,18 +1131,18 @@
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
@@ -905,18 +1151,18 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>10</v>
@@ -925,18 +1171,18 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>10</v>
@@ -945,18 +1191,18 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>10</v>
@@ -965,18 +1211,18 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>10</v>
@@ -985,18 +1231,18 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>10</v>
@@ -1005,18 +1251,18 @@
         <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" ht="118" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" ht="136" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>10</v>
@@ -1025,18 +1271,18 @@
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>10</v>
@@ -1045,18 +1291,18 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>10</v>
@@ -1065,18 +1311,18 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" ht="118" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>10</v>
@@ -1085,18 +1331,18 @@
         <v>11</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>10</v>
@@ -1105,18 +1351,18 @@
         <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>10</v>
@@ -1125,18 +1371,18 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>10</v>
@@ -1145,18 +1391,18 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>10</v>
@@ -1165,18 +1411,18 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>10</v>
@@ -1185,18 +1431,18 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
@@ -1205,18 +1451,18 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>10</v>
@@ -1225,18 +1471,18 @@
         <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
@@ -1245,18 +1491,18 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
@@ -1265,18 +1511,18 @@
         <v>11</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>10</v>
@@ -1285,18 +1531,18 @@
         <v>11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>10</v>
@@ -1305,18 +1551,18 @@
         <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
@@ -1325,18 +1571,18 @@
         <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>10</v>
@@ -1345,17 +1591,457 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F38"/>
+  <autoFilter ref="A5:F60"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>

--- a/translations/welsh-translations/xlsx/18-obligations-home.xlsx
+++ b/translations/welsh-translations/xlsx/18-obligations-home.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="161">
   <si>
     <t>Translator notes</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>obligations.home.statementMissedDeadlineParagraphPrefix</t>
+  </si>
+  <si>
+    <t>You missed the submission deadline of 31 January {{year}}. You can no longer submit your {{yearBefore}} statement of compliance.</t>
   </si>
   <si>
     <t>obligations.home.statementMissedDeadlineParagraphSuffix</t>
@@ -1771,7 +1774,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>14</v>
@@ -1782,7 +1785,7 @@
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>10</v>
@@ -1802,7 +1805,7 @@
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>10</v>
@@ -1811,10 +1814,10 @@
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>14</v>
@@ -1822,7 +1825,7 @@
     </row>
     <row r="50" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>10</v>
@@ -1831,10 +1834,10 @@
         <v>11</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>14</v>
@@ -1842,7 +1845,7 @@
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>10</v>
@@ -1851,10 +1854,10 @@
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>14</v>
@@ -1862,7 +1865,7 @@
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>10</v>
@@ -1871,10 +1874,10 @@
         <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>14</v>
@@ -1882,7 +1885,7 @@
     </row>
     <row r="53" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>10</v>
@@ -1891,10 +1894,10 @@
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>14</v>
@@ -1902,7 +1905,7 @@
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>10</v>
@@ -1911,10 +1914,10 @@
         <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>14</v>
@@ -1922,7 +1925,7 @@
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>10</v>
@@ -1942,7 +1945,7 @@
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>10</v>
@@ -1951,7 +1954,7 @@
         <v>11</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>14</v>
@@ -1962,7 +1965,7 @@
     </row>
     <row r="57" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>10</v>
@@ -1971,7 +1974,7 @@
         <v>11</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>14</v>
@@ -1982,7 +1985,7 @@
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>10</v>
@@ -2002,7 +2005,7 @@
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>10</v>
@@ -2011,7 +2014,7 @@
         <v>11</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>14</v>
@@ -2022,7 +2025,7 @@
     </row>
     <row r="60" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>10</v>
@@ -2031,7 +2034,7 @@
         <v>11</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>14</v>
